--- a/Assets/Data/Dungeon2010.xlsx
+++ b/Assets/Data/Dungeon2010.xlsx
@@ -102,10 +102,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -123,17 +123,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -147,29 +138,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,30 +181,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,30 +206,46 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,10 +260,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -276,7 +276,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,7 +288,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,31 +360,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,13 +378,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,13 +402,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -372,49 +438,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,37 +450,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,6 +467,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -481,6 +490,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,9 +535,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,30 +549,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -556,17 +567,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -575,145 +575,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon2010.xlsx
+++ b/Assets/Data/Dungeon2010.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -102,10 +102,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -123,8 +123,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -138,36 +147,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,6 +185,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -188,23 +200,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -220,25 +229,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,18 +245,25 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -276,13 +276,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,7 +306,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,67 +354,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,7 +384,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,19 +420,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,19 +444,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,19 +456,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,15 +467,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -490,56 +481,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -567,6 +508,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -575,67 +575,67 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -644,76 +644,76 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1355,13 +1355,13 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1464,13 +1464,13 @@
         <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>8</v>
@@ -1532,31 +1532,31 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>8</v>
@@ -1609,31 +1609,25 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
@@ -1686,31 +1680,31 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>8</v>
@@ -1763,31 +1757,29 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>8</v>
@@ -1840,31 +1832,31 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>8</v>
@@ -1928,9 +1920,7 @@
       <c r="H8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
@@ -2002,9 +1992,15 @@
       <c r="G9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
@@ -2067,27 +2063,13 @@
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2144,21 +2126,17 @@
       <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
         <v>9</v>
       </c>
@@ -2215,27 +2193,13 @@
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2298,13 +2262,9 @@
       <c r="G13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
         <v>9</v>
       </c>
@@ -2373,15 +2333,9 @@
       <c r="G14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2643,9 +2597,13 @@
       <c r="G18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K18" s="2" t="s">
         <v>9</v>
       </c>
@@ -2706,25 +2664,29 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>8</v>
@@ -2777,17 +2739,31 @@
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="M20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>8</v>
@@ -2830,44 +2806,22 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-      <c r="M21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
@@ -2897,18 +2851,10 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -2916,21 +2862,11 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-      <c r="M22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
@@ -2960,52 +2896,22 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
@@ -3035,52 +2941,22 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
@@ -3110,54 +2986,22 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
@@ -3953,13 +3797,13 @@
         <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>8</v>
@@ -4021,31 +3865,29 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>8</v>
@@ -4098,31 +3940,25 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
@@ -4175,31 +4011,31 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>8</v>
@@ -4252,31 +4088,31 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>8</v>
@@ -4329,31 +4165,31 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>8</v>
@@ -4489,9 +4325,15 @@
       <c r="G9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
@@ -4555,25 +4397,25 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
@@ -4632,25 +4474,25 @@
         <v>9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>9</v>
@@ -4709,25 +4551,25 @@
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
@@ -4792,11 +4634,13 @@
         <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="J13" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>9</v>
@@ -4867,13 +4711,13 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>9</v>
@@ -5175,13 +5019,11 @@
         <v>9</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>9</v>
@@ -5243,31 +5085,29 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>8</v>
@@ -5320,31 +5160,31 @@
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>8</v>
@@ -5387,54 +5227,22 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
@@ -5464,54 +5272,22 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
@@ -5541,52 +5317,22 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
@@ -5616,52 +5362,22 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
@@ -5691,54 +5407,22 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
@@ -6495,7 +6179,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -6528,7 +6212,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -6561,7 +6245,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -6594,7 +6278,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>3010</v>
@@ -6627,7 +6311,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>3010</v>
@@ -6660,7 +6344,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>3010</v>
@@ -6693,7 +6377,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>3010</v>
@@ -6726,7 +6410,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>3010</v>
@@ -6759,7 +6443,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>3010</v>
@@ -6792,7 +6476,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>3010</v>
@@ -6825,7 +6509,7 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>3010</v>
@@ -6858,7 +6542,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>3010</v>
@@ -6891,7 +6575,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>3010</v>
